--- a/artfynd/A 13073-2023 artfynd.xlsx
+++ b/artfynd/A 13073-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116392061</v>
+        <v>116392641</v>
       </c>
       <c r="B2" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Baggetorp fotbollsplan (Baggetorp), Srm</t>
+          <t>Nedre Sjögölet, Nedre Sjögölet, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560533</v>
+        <v>560316</v>
       </c>
       <c r="R2" t="n">
-        <v>6540992</v>
+        <v>6541140</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera tallar med tallticka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,62 +796,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116391377</v>
+        <v>116393230</v>
       </c>
       <c r="B3" t="n">
-        <v>57296</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Baggetorp fotbollsplan (Baggetorp), Srm</t>
+          <t>Nedre Sjögölet, Nedre Sjögölet, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560584</v>
+        <v>560343</v>
       </c>
       <c r="R3" t="n">
-        <v>6541186</v>
+        <v>6541160</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116391717</v>
+        <v>116393374</v>
       </c>
       <c r="B4" t="n">
-        <v>56742</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,51 +923,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102961</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrängsviken (Norrängsviken), Srm</t>
+          <t>Nedre Sjögölet, Nedre Sjögölet, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560420</v>
+        <v>560336</v>
       </c>
       <c r="R4" t="n">
-        <v>6541035</v>
+        <v>6541155</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,15 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116391824</v>
+        <v>116392061</v>
       </c>
       <c r="B5" t="n">
-        <v>57636</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,16 +1039,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1083,22 +1063,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Sjögölet (Nedre Sjögölet), Srm</t>
+          <t>Baggetorp fotbollsplan, Baggetorp, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560396</v>
+        <v>560533</v>
       </c>
       <c r="R5" t="n">
-        <v>6541057</v>
+        <v>6540992</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1137,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,62 +1144,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116392641</v>
+        <v>116395066</v>
       </c>
       <c r="B6" t="n">
-        <v>90462</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Sjögölet (Nedre Sjögölet), Srm</t>
+          <t>Baggetorp fotbollsplan, Baggetorp, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560316</v>
+        <v>560593</v>
       </c>
       <c r="R6" t="n">
-        <v>6541140</v>
+        <v>6541037</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1248,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:38</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera tallar med tallticka</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,15 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116393738</v>
+        <v>116397100</v>
       </c>
       <c r="B7" t="n">
-        <v>57928</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>100065</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1328,26 +1293,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre Sjögölet (Nedre Sjögölet), Srm</t>
+          <t>Nedre Sjögölet, Nedre Sjögölet, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560381</v>
+        <v>560371</v>
       </c>
       <c r="R7" t="n">
-        <v>6541122</v>
+        <v>6541194</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1379,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1389,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,15 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116391712</v>
+        <v>117277331</v>
       </c>
       <c r="B8" t="n">
-        <v>56924</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,16 +1387,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102964</v>
+        <v>102119</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1451,24 +1406,24 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrängsviken (Norrängsviken), Srm</t>
+          <t>Nedre Sjögölet, Nedre Sjögölet, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560420</v>
+        <v>560268</v>
       </c>
       <c r="R8" t="n">
-        <v>6541035</v>
+        <v>6541132</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1495,22 +1450,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,37 +1492,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116394556</v>
+        <v>116391717</v>
       </c>
       <c r="B9" t="n">
-        <v>57636</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>102961</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1575,21 +1525,26 @@
           <t>2</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Baggetorp fotbollsplan (Baggetorp), Srm</t>
+          <t>Norrängsviken, Norrängsviken, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560561</v>
+        <v>560420</v>
       </c>
       <c r="R9" t="n">
-        <v>6541020</v>
+        <v>6541035</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1621,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1631,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,37 +1613,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116395066</v>
+        <v>116391377</v>
       </c>
       <c r="B10" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1698,22 +1648,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Baggetorp fotbollsplan (Baggetorp), Srm</t>
+          <t>Baggetorp fotbollsplan, Baggetorp, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560593</v>
+        <v>560584</v>
       </c>
       <c r="R10" t="n">
-        <v>6541037</v>
+        <v>6541186</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1742,7 +1692,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1752,7 +1702,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,15 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117276932</v>
+        <v>116393270</v>
       </c>
       <c r="B11" t="n">
-        <v>57768</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,21 +1740,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>102980</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1817,26 +1762,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Baggetorp fotbollsplan (Baggetorp), Srm</t>
+          <t>Nedre Sjögölet, Nedre Sjögölet, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560486</v>
+        <v>560336</v>
       </c>
       <c r="R11" t="n">
-        <v>6541043</v>
+        <v>6541149</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1863,22 +1803,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1905,15 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117276931</v>
+        <v>116391824</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,17 +1885,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Baggetorp fotbollsplan (Baggetorp), Srm</t>
+          <t>Nedre Sjögölet, Nedre Sjögölet, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560486</v>
+        <v>560396</v>
       </c>
       <c r="R12" t="n">
-        <v>6541043</v>
+        <v>6541057</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1984,22 +1919,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,47 +1961,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117276666</v>
+        <v>116394556</v>
       </c>
       <c r="B13" t="n">
-        <v>57768</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2076,14 +2001,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Baggetorp fotbollsplan (Baggetorp), Srm</t>
+          <t>Baggetorp fotbollsplan, Baggetorp, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560579</v>
+        <v>560561</v>
       </c>
       <c r="R13" t="n">
-        <v>6541165</v>
+        <v>6541020</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2110,22 +2035,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>04:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>04:53</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2149,6 +2074,717 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>117276931</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Baggetorp fotbollsplan, Baggetorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>560486</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6541043</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>117276666</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Baggetorp fotbollsplan, Baggetorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>560579</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6541165</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>04:53</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>04:53</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>117276932</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Baggetorp fotbollsplan, Baggetorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>560486</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6541043</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>116392835</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nedre Sjögölet, Nedre Sjögölet, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>560314</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6541150</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>116393738</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nedre Sjögölet, Nedre Sjögölet, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>560381</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6541122</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>116392017</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nedre Sjögölet, Nedre Sjögölet, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>560369</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6541048</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Västra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13073-2023 artfynd.xlsx
+++ b/artfynd/A 13073-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116392641</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116393230</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116393374</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116392061</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116395066</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,6 +1403,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116397100</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1489,6 +1524,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117277331</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1610,6 +1650,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116391717</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1726,6 +1771,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116391377</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1842,6 +1892,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116393270</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1958,6 +2013,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116391824</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2074,6 +2134,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116394556</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2190,6 +2255,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117276931</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2311,6 +2381,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117276666</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2432,6 +2507,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117276932</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2548,6 +2628,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116392835</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2669,6 +2754,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116393738</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2785,8 +2875,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116392017</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>